--- a/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:13:46-03:00</t>
+    <t>2026-09-15T10:16:15-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T10:16:15-03:00</t>
+    <t>2026-09-21T17:12:23-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/ValueSet-motivo-cancelacion-solicitud-laboratorio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T17:12:23-03:00</t>
+    <t>2026-09-22T09:29:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Motivo por el cual una solicitud de laboratorio se cancela antes de la toma de muestra, sin que exista un Specimen asociado (por ejemplo, el paciente no concurre a la toma de muestra). Este ValueSet no define códigos propios; referencia el CodeSystem externo SNOMED CT. Binding extensible: permite agregar otros códigos SNOMED CT si se identifican nuevos motivos de cancelación sin muestra.</t>
+    <t>Motivo por el cual una solicitud de laboratorio se cancela antes de la toma de muestra, sin que exista un Specimen asociado (por ejemplo, el paciente no concurre a la toma de muestra). Referencia el código local `no-presentacion` del CodeSystem MINSAL `CSMotivoAdministrativoCancelacionLaboratorio`, creado porque el concepto SNOMED CT usado originalmente para este motivo (270426007) fue inactivado por SNOMED International sin reemplazo directo (ver descripción del CodeSystem). Binding extensible: permite agregar otros códigos, locales o de catálogos externos, si se identifican nuevos motivos de cancelación sin muestra.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,10 +102,10 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>270426007</t>
-  </si>
-  <si>
-    <t>Did not attend - no reason</t>
+    <t>no-presentacion</t>
+  </si>
+  <si>
+    <t>Paciente no se presenta (sin motivo informado)</t>
   </si>
   <si>
     <t/>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://snomed.info/sct</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/CodeSystem/motivo-administrativo-cancelacion-laboratorio</t>
   </si>
 </sst>
 </file>
